--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -2491,7 +2491,7 @@
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>37645.0</v>
+        <v>37378.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -3424,10 +3424,10 @@
         <v>46</v>
       </c>
       <c r="F124" t="n">
-        <v>2049.0</v>
+        <v>2310.0</v>
       </c>
       <c r="G124" t="n">
-        <v>197962.0</v>
+        <v>197701.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>11434.0</v>
+        <v>10484.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -3479,10 +3479,10 @@
         <v>241.0</v>
       </c>
       <c r="G126" t="n">
-        <v>578258.0</v>
+        <v>578989.0</v>
       </c>
       <c r="H126" t="n">
-        <v>731.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1295,7 +1295,7 @@
         <v>15.0</v>
       </c>
       <c r="G42" t="n">
-        <v>13145.0</v>
+        <v>12406.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -2000,7 +2000,7 @@
         <v>544616.0</v>
       </c>
       <c r="H69" t="n">
-        <v>69396.0</v>
+        <v>66329.0</v>
       </c>
     </row>
     <row r="70">

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3479,7 +3479,7 @@
         <v>241.0</v>
       </c>
       <c r="G126" t="n">
-        <v>578989.0</v>
+        <v>577994.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -1425,7 +1425,7 @@
         <v>28.0</v>
       </c>
       <c r="G47" t="n">
-        <v>41396.0</v>
+        <v>42583.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1477,7 +1477,7 @@
         <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>148038.0</v>
+        <v>151149.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1948,7 +1948,7 @@
         <v>162125.0</v>
       </c>
       <c r="H67" t="n">
-        <v>71029.0</v>
+        <v>73361.0</v>
       </c>
     </row>
     <row r="68">
@@ -2075,7 +2075,7 @@
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>136014.0</v>
+        <v>141196.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2387,7 +2387,7 @@
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2595,10 +2595,10 @@
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
       <c r="H92" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="93">
@@ -2621,7 +2621,7 @@
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="H93" t="n">
         <v>3.0</v>
@@ -3427,7 +3427,7 @@
         <v>2310.0</v>
       </c>
       <c r="G124" t="n">
-        <v>197701.0</v>
+        <v>210219.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3450,10 +3450,10 @@
         <v>42</v>
       </c>
       <c r="F125" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>51.0</v>
+        <v>57.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3479,7 +3479,7 @@
         <v>241.0</v>
       </c>
       <c r="G126" t="n">
-        <v>577994.0</v>
+        <v>585110.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3724,19 +3724,19 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0</v>
+        <v>45.0</v>
       </c>
       <c r="G136" t="n">
         <v>0.0</v>
@@ -3750,22 +3750,22 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G137" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3776,22 +3776,22 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="G138" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3802,22 +3802,22 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>1770.0</v>
       </c>
       <c r="G139" t="n">
-        <v>49.0</v>
+        <v>3356.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3828,22 +3828,22 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F140" t="n">
-        <v>9.0</v>
+        <v>46.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>69.0</v>
       </c>
       <c r="H140" t="n">
         <v>0.0</v>
@@ -3854,22 +3854,22 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
         <v>42</v>
       </c>
       <c r="F141" t="n">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="G141" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n">
         <v>0.0</v>
@@ -3880,22 +3880,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F142" t="n">
-        <v>8.0</v>
+        <v>184.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>667.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,25 +3906,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E143" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0</v>
+        <v>201.0</v>
       </c>
       <c r="G143" t="n">
-        <v>58.0</v>
+        <v>0.0</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="144">
@@ -3932,7 +3932,7 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3941,13 +3941,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G144" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3958,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3967,13 +3967,13 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F145" t="n">
         <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>77.0</v>
+        <v>7.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3984,7 +3984,7 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3993,13 +3993,13 @@
         <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,22 +4010,22 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F147" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
       <c r="G147" t="n">
-        <v>19.0</v>
+        <v>49.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4042,16 +4042,16 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F148" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G148" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4068,16 +4068,16 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4094,16 +4094,16 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G150" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,22 +4114,22 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E151" t="s">
         <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
-        <v>27.0</v>
+        <v>8.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,22 +4140,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4166,22 +4166,22 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F153" t="n">
         <v>0.0</v>
       </c>
       <c r="G153" t="n">
-        <v>3.0</v>
+        <v>126.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4198,16 +4198,16 @@
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E154" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="G154" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4218,22 +4218,22 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F155" t="n">
-        <v>3.0</v>
+        <v>38.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,22 +4244,22 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F156" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,22 +4270,22 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
       </c>
       <c r="D157" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F157" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G157" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>17.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,22 +4296,22 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F158" t="n">
         <v>0.0</v>
       </c>
       <c r="G158" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4322,22 +4322,22 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
       </c>
       <c r="D159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0</v>
+        <v>51.0</v>
       </c>
       <c r="G159" t="n">
-        <v>51.0</v>
+        <v>27.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,19 +4348,19 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F160" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -4374,22 +4374,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E161" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>155.0</v>
+        <v>0.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4400,22 +4400,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F162" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>14.0</v>
+        <v>31.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4432,16 +4432,16 @@
         <v>17</v>
       </c>
       <c r="D163" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F163" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G163" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4458,16 +4458,16 @@
         <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F164" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="G164" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4478,22 +4478,22 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F165" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G165" t="n">
         <v>17.0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4504,22 +4504,22 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
       </c>
       <c r="D166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F166" t="n">
         <v>0.0</v>
       </c>
       <c r="G166" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4536,16 +4536,16 @@
         <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F167" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G167" t="n">
-        <v>9.0</v>
+        <v>51.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4556,22 +4556,22 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
       </c>
       <c r="D168" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F168" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G168" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4582,22 +4582,22 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G169" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4608,22 +4608,22 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0</v>
+        <v>502.0</v>
       </c>
       <c r="G170" t="n">
-        <v>528.0</v>
+        <v>5322.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4634,22 +4634,22 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E171" t="s">
         <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0</v>
+        <v>111.0</v>
       </c>
       <c r="G171" t="n">
-        <v>1.0</v>
+        <v>65.0</v>
       </c>
       <c r="H171" t="n">
         <v>0.0</v>
@@ -4660,22 +4660,22 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E172" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F172" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H172" t="n">
         <v>0.0</v>
@@ -4686,22 +4686,22 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E173" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F173" t="n">
-        <v>4.0</v>
+        <v>31.0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0</v>
+        <v>663.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4712,22 +4712,22 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E174" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F174" t="n">
-        <v>91.0</v>
+        <v>396.0</v>
       </c>
       <c r="G174" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4738,22 +4738,22 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
       </c>
       <c r="D175" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F175" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G175" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4764,19 +4764,19 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
       </c>
       <c r="D176" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F176" t="n">
-        <v>153.0</v>
+        <v>155.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4790,24 +4790,414 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>40</v>
+      </c>
+      <c r="E177" t="s">
+        <v>43</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>40</v>
+      </c>
+      <c r="E178" t="s">
+        <v>44</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>40</v>
+      </c>
+      <c r="E179" t="s">
+        <v>45</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>40</v>
+      </c>
+      <c r="E180" t="s">
+        <v>46</v>
+      </c>
+      <c r="F180" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>40</v>
+      </c>
+      <c r="E181" t="s">
+        <v>42</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>41</v>
+      </c>
+      <c r="E182" t="s">
+        <v>49</v>
+      </c>
+      <c r="F182" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>41</v>
+      </c>
+      <c r="E183" t="s">
+        <v>43</v>
+      </c>
+      <c r="F183" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>41</v>
+      </c>
+      <c r="E184" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>41</v>
+      </c>
+      <c r="E185" t="s">
+        <v>44</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>535.0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>41</v>
+      </c>
+      <c r="E186" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
         <v>10</v>
       </c>
-      <c r="C177" t="s">
-        <v>17</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
         <v>41</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E187" t="s">
+        <v>49</v>
+      </c>
+      <c r="F187" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>41</v>
+      </c>
+      <c r="E188" t="s">
+        <v>47</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" t="s">
+        <v>46</v>
+      </c>
+      <c r="F189" t="n">
+        <v>91.0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" t="s">
+        <v>43</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" t="s">
+        <v>44</v>
+      </c>
+      <c r="F191" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>41</v>
+      </c>
+      <c r="E192" t="s">
         <v>45</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F192" t="n">
         <v>5.0</v>
       </c>
-      <c r="G177" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H177" t="n">
+      <c r="G192" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H192" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1997,7 +1997,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>544616.0</v>
+        <v>537234.0</v>
       </c>
       <c r="H69" t="n">
         <v>66329.0</v>
@@ -3453,7 +3453,7 @@
         <v>12.0</v>
       </c>
       <c r="G125" t="n">
-        <v>57.0</v>
+        <v>51.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3609,7 +3609,7 @@
         <v>35.0</v>
       </c>
       <c r="G131" t="n">
-        <v>23619.0</v>
+        <v>17659.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1295,7 +1295,7 @@
         <v>15.0</v>
       </c>
       <c r="G42" t="n">
-        <v>12406.0</v>
+        <v>10703.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3479,7 +3479,7 @@
         <v>241.0</v>
       </c>
       <c r="G126" t="n">
-        <v>585110.0</v>
+        <v>586105.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3427,7 +3427,7 @@
         <v>2310.0</v>
       </c>
       <c r="G124" t="n">
-        <v>210219.0</v>
+        <v>210270.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3479,7 +3479,7 @@
         <v>241.0</v>
       </c>
       <c r="G126" t="n">
-        <v>586105.0</v>
+        <v>583985.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -2023,7 +2023,7 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>121650.0</v>
+        <v>119869.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2696,10 +2696,10 @@
         <v>42</v>
       </c>
       <c r="F96" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G96" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2777,7 +2777,7 @@
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1710.0</v>
+        <v>4984.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2797,13 +2797,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>3913.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2814,7 +2814,7 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -2823,13 +2823,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>3274.0</v>
+        <v>16.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2849,13 +2849,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>3913.0</v>
+        <v>3474.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2866,25 +2866,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" t="s">
         <v>42</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G103" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="104">
@@ -2892,22 +2892,22 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C104" t="s">
         <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
       </c>
       <c r="G104" t="n">
-        <v>3474.0</v>
+        <v>381.0</v>
       </c>
       <c r="H104" t="n">
         <v>0.0</v>
@@ -2927,16 +2927,16 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>6.0</v>
+        <v>265.0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -2944,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2959,7 +2959,7 @@
         <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>381.0</v>
+        <v>70.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2970,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -2979,16 +2979,16 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>265.0</v>
+        <v>3.0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="108">
@@ -2996,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -3005,13 +3005,13 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H108" t="n">
         <v>0.0</v>
@@ -3022,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3034,10 +3034,10 @@
         <v>46</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0</v>
+        <v>147.0</v>
       </c>
       <c r="G109" t="n">
-        <v>70.0</v>
+        <v>3034.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3048,7 +3048,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -3060,13 +3060,13 @@
         <v>42</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="H110" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3083,13 +3083,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F111" t="n">
-        <v>12.0</v>
+        <v>42.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>11839.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,22 +3100,22 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E112" t="s">
         <v>46</v>
       </c>
       <c r="F112" t="n">
-        <v>147.0</v>
+        <v>45.0</v>
       </c>
       <c r="G112" t="n">
-        <v>3034.0</v>
+        <v>23875.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3126,22 +3126,22 @@
         <v>8</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E113" t="s">
         <v>42</v>
       </c>
       <c r="F113" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="G113" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3152,22 +3152,22 @@
         <v>8</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E114" t="s">
         <v>44</v>
       </c>
       <c r="F114" t="n">
-        <v>42.0</v>
+        <v>737.0</v>
       </c>
       <c r="G114" t="n">
-        <v>11839.0</v>
+        <v>48265.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3187,13 +3187,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
-        <v>45.0</v>
+        <v>4.0</v>
       </c>
       <c r="G115" t="n">
-        <v>23875.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3213,13 +3213,13 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F116" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="G116" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3230,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3239,13 +3239,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F117" t="n">
-        <v>737.0</v>
+        <v>22.0</v>
       </c>
       <c r="G117" t="n">
-        <v>48265.0</v>
+        <v>3824.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3256,7 +3256,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
@@ -3265,13 +3265,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3291,13 +3291,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>922.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3317,16 +3317,16 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F120" t="n">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>3824.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="121">
@@ -3334,7 +3334,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -3343,13 +3343,13 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0</v>
+        <v>2310.0</v>
       </c>
       <c r="G121" t="n">
-        <v>3.0</v>
+        <v>210270.0</v>
       </c>
       <c r="H121" t="n">
         <v>0.0</v>
@@ -3360,7 +3360,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
@@ -3369,13 +3369,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G122" t="n">
-        <v>922.0</v>
+        <v>51.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3395,16 +3395,16 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0</v>
+        <v>583985.0</v>
       </c>
       <c r="H123" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3421,13 +3421,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F124" t="n">
-        <v>2310.0</v>
+        <v>4.0</v>
       </c>
       <c r="G124" t="n">
-        <v>210270.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3444,16 +3444,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F125" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="G125" t="n">
-        <v>51.0</v>
+        <v>81.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3470,16 +3470,16 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F126" t="n">
-        <v>241.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" t="n">
-        <v>583985.0</v>
+        <v>0.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3496,16 +3496,16 @@
         <v>16</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F127" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3525,13 +3525,13 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F128" t="n">
-        <v>4.0</v>
+        <v>35.0</v>
       </c>
       <c r="G128" t="n">
-        <v>81.0</v>
+        <v>17659.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3548,16 +3548,16 @@
         <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E129" t="s">
         <v>46</v>
       </c>
       <c r="F129" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>7663.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3574,19 +3574,19 @@
         <v>16</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E130" t="s">
         <v>42</v>
       </c>
       <c r="F130" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="H130" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -3600,16 +3600,16 @@
         <v>16</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
         <v>44</v>
       </c>
       <c r="F131" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>17659.0</v>
+        <v>16248.0</v>
       </c>
       <c r="H131" t="n">
         <v>0.0</v>
@@ -3620,22 +3620,22 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E132" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G132" t="n">
-        <v>7663.0</v>
+        <v>11.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3649,22 +3649,22 @@
         <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>45.0</v>
       </c>
       <c r="G133" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="134">
@@ -3675,19 +3675,19 @@
         <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G134" t="n">
-        <v>16248.0</v>
+        <v>3.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3698,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3707,13 +3707,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F135" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="G135" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3733,13 +3733,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F136" t="n">
-        <v>45.0</v>
+        <v>1770.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>3356.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3759,13 +3759,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F137" t="n">
-        <v>4.0</v>
+        <v>46.0</v>
       </c>
       <c r="G137" t="n">
-        <v>3.0</v>
+        <v>69.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3785,10 +3785,10 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F138" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -3811,13 +3811,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F139" t="n">
-        <v>1770.0</v>
+        <v>184.0</v>
       </c>
       <c r="G139" t="n">
-        <v>3356.0</v>
+        <v>667.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3837,16 +3837,16 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F140" t="n">
-        <v>46.0</v>
+        <v>201.0</v>
       </c>
       <c r="G140" t="n">
-        <v>69.0</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="141">
@@ -3854,19 +3854,19 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F141" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3880,22 +3880,22 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F142" t="n">
-        <v>184.0</v>
+        <v>0.0</v>
       </c>
       <c r="G142" t="n">
-        <v>667.0</v>
+        <v>7.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3906,25 +3906,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n">
-        <v>201.0</v>
+        <v>0.0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H143" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="144">
@@ -3941,13 +3941,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3958,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3967,13 +3967,13 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="G145" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3984,7 +3984,7 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3996,10 +3996,10 @@
         <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="G146" t="n">
-        <v>7.0</v>
+        <v>24.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4010,7 +4010,7 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -4019,13 +4019,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G147" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4045,13 +4045,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F148" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4071,13 +4071,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F149" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>24.0</v>
+        <v>11.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4097,13 +4097,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F150" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>126.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,7 +4114,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4126,10 +4126,10 @@
         <v>46</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="G151" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4146,16 +4146,16 @@
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
       <c r="G152" t="n">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4172,16 +4172,16 @@
         <v>17</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="n">
-        <v>126.0</v>
+        <v>7.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4192,22 +4192,22 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F154" t="n">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4227,13 +4227,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F155" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,7 +4244,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4253,13 +4253,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F156" t="n">
-        <v>1.0</v>
+        <v>51.0</v>
       </c>
       <c r="G156" t="n">
-        <v>7.0</v>
+        <v>27.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4270,7 +4270,7 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
@@ -4279,13 +4279,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G157" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4296,7 +4296,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -4305,13 +4305,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F158" t="n">
         <v>0.0</v>
       </c>
       <c r="G158" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4331,13 +4331,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F159" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="G159" t="n">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,19 +4348,19 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E160" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F160" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -4374,22 +4374,22 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G161" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4400,22 +4400,22 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
-        <v>31.0</v>
+        <v>17.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4435,13 +4435,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F163" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4461,13 +4461,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>2.0</v>
+        <v>51.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4478,7 +4478,7 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -4487,13 +4487,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F165" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G165" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4504,7 +4504,7 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4513,13 +4513,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G166" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -4539,13 +4539,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0</v>
+        <v>502.0</v>
       </c>
       <c r="G167" t="n">
-        <v>51.0</v>
+        <v>5322.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4565,13 +4565,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>6.0</v>
+        <v>111.0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0</v>
+        <v>65.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4591,13 +4591,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G169" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4617,13 +4617,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>502.0</v>
+        <v>31.0</v>
       </c>
       <c r="G170" t="n">
-        <v>5322.0</v>
+        <v>663.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4643,13 +4643,13 @@
         <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F171" t="n">
-        <v>111.0</v>
+        <v>396.0</v>
       </c>
       <c r="G171" t="n">
-        <v>65.0</v>
+        <v>0.0</v>
       </c>
       <c r="H171" t="n">
         <v>0.0</v>
@@ -4660,22 +4660,22 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G172" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H172" t="n">
         <v>0.0</v>
@@ -4686,22 +4686,22 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F173" t="n">
-        <v>31.0</v>
+        <v>155.0</v>
       </c>
       <c r="G173" t="n">
-        <v>663.0</v>
+        <v>0.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4712,22 +4712,22 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
       </c>
       <c r="D174" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F174" t="n">
-        <v>396.0</v>
+        <v>4.0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4747,13 +4747,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F175" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4773,10 +4773,10 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F176" t="n">
-        <v>155.0</v>
+        <v>2.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4790,7 +4790,7 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C177" t="s">
         <v>17</v>
@@ -4799,13 +4799,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F177" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="G177" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4816,7 +4816,7 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
@@ -4825,13 +4825,13 @@
         <v>40</v>
       </c>
       <c r="E178" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F178" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G178" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>18.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4848,16 +4848,16 @@
         <v>17</v>
       </c>
       <c r="D179" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F179" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4868,22 +4868,22 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
         <v>17</v>
       </c>
       <c r="D180" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F180" t="n">
-        <v>17.0</v>
+        <v>3.0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4894,13 +4894,13 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C181" t="s">
         <v>17</v>
       </c>
       <c r="D181" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E181" t="s">
         <v>42</v>
@@ -4909,7 +4909,7 @@
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4929,13 +4929,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F182" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>9.0</v>
+        <v>535.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4946,7 +4946,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4958,10 +4958,10 @@
         <v>43</v>
       </c>
       <c r="F183" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G183" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4972,7 +4972,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -4981,13 +4981,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G184" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -4998,7 +4998,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C185" t="s">
         <v>17</v>
@@ -5007,13 +5007,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G185" t="n">
-        <v>535.0</v>
+        <v>0.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5024,7 +5024,7 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C186" t="s">
         <v>17</v>
@@ -5033,13 +5033,13 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0</v>
+        <v>91.0</v>
       </c>
       <c r="G186" t="n">
-        <v>1.0</v>
+        <v>64.0</v>
       </c>
       <c r="H186" t="n">
         <v>0.0</v>
@@ -5059,13 +5059,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F187" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5085,10 +5085,10 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F188" t="n">
-        <v>4.0</v>
+        <v>153.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
@@ -5111,93 +5111,15 @@
         <v>41</v>
       </c>
       <c r="E189" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F189" t="n">
-        <v>91.0</v>
+        <v>5.0</v>
       </c>
       <c r="G189" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
       <c r="H189" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>8</v>
-      </c>
-      <c r="B190" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>41</v>
-      </c>
-      <c r="E190" t="s">
-        <v>43</v>
-      </c>
-      <c r="F190" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G190" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="H190" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>8</v>
-      </c>
-      <c r="B191" t="s">
-        <v>10</v>
-      </c>
-      <c r="C191" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" t="s">
-        <v>41</v>
-      </c>
-      <c r="E191" t="s">
-        <v>44</v>
-      </c>
-      <c r="F191" t="n">
-        <v>153.0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>8</v>
-      </c>
-      <c r="B192" t="s">
-        <v>10</v>
-      </c>
-      <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>41</v>
-      </c>
-      <c r="E192" t="s">
-        <v>45</v>
-      </c>
-      <c r="F192" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H192" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>583985.0</v>
+        <v>583490.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -4389,7 +4389,7 @@
         <v>8.0</v>
       </c>
       <c r="G161" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>10484.0</v>
+        <v>9684.0</v>
       </c>
       <c r="H15" t="n">
         <v>0.0</v>
@@ -4542,7 +4542,7 @@
         <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>502.0</v>
+        <v>471.0</v>
       </c>
       <c r="G167" t="n">
         <v>5322.0</v>
@@ -4568,7 +4568,7 @@
         <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>111.0</v>
+        <v>142.0</v>
       </c>
       <c r="G168" t="n">
         <v>65.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1974,7 +1974,7 @@
         <v>35.0</v>
       </c>
       <c r="H68" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="69">

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1295,7 +1295,7 @@
         <v>15.0</v>
       </c>
       <c r="G42" t="n">
-        <v>10703.0</v>
+        <v>10702.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -4103,7 +4103,7 @@
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>126.0</v>
+        <v>118.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3346,7 +3346,7 @@
         <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>2310.0</v>
+        <v>1518.0</v>
       </c>
       <c r="G121" t="n">
         <v>210270.0</v>
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>583490.0</v>
+        <v>582436.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -437,7 +437,7 @@
         <v>1.0</v>
       </c>
       <c r="G9" t="n">
-        <v>24416.0</v>
+        <v>24406.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -853,7 +853,7 @@
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>38352.0</v>
+        <v>37865.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>537234.0</v>
+        <v>534439.0</v>
       </c>
       <c r="H69" t="n">
         <v>66329.0</v>
@@ -4357,10 +4357,10 @@
         <v>39</v>
       </c>
       <c r="E160" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F160" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -4383,13 +4383,13 @@
         <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F161" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4409,13 +4409,13 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F162" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G162" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H162" t="n">
         <v>0.0</v>
@@ -4435,13 +4435,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F163" t="n">
         <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>16.0</v>
+        <v>51.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4452,7 +4452,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4461,13 +4461,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G164" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4487,13 +4487,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F165" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4513,13 +4513,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F166" t="n">
-        <v>4.0</v>
+        <v>471.0</v>
       </c>
       <c r="G166" t="n">
-        <v>4.0</v>
+        <v>5322.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4539,13 +4539,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F167" t="n">
-        <v>471.0</v>
+        <v>142.0</v>
       </c>
       <c r="G167" t="n">
-        <v>5322.0</v>
+        <v>65.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4565,13 +4565,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F168" t="n">
-        <v>142.0</v>
+        <v>3.0</v>
       </c>
       <c r="G168" t="n">
-        <v>65.0</v>
+        <v>7.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4591,13 +4591,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F169" t="n">
-        <v>3.0</v>
+        <v>31.0</v>
       </c>
       <c r="G169" t="n">
-        <v>7.0</v>
+        <v>663.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4617,13 +4617,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F170" t="n">
-        <v>31.0</v>
+        <v>396.0</v>
       </c>
       <c r="G170" t="n">
-        <v>663.0</v>
+        <v>0.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4634,19 +4634,19 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E171" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F171" t="n">
-        <v>396.0</v>
+        <v>9.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -4669,10 +4669,10 @@
         <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F172" t="n">
-        <v>9.0</v>
+        <v>155.0</v>
       </c>
       <c r="G172" t="n">
         <v>0.0</v>
@@ -4695,13 +4695,13 @@
         <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F173" t="n">
-        <v>155.0</v>
+        <v>4.0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4721,13 +4721,13 @@
         <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F174" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G174" t="n">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4747,13 +4747,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F175" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G175" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4764,7 +4764,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4773,10 +4773,10 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F176" t="n">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4799,13 +4799,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F177" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4816,22 +4816,22 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E178" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4851,13 +4851,13 @@
         <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F179" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G179" t="n">
         <v>13.0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>9.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4877,13 +4877,13 @@
         <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F180" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G180" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4903,13 +4903,13 @@
         <v>41</v>
       </c>
       <c r="E181" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F181" t="n">
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>4.0</v>
+        <v>535.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4920,7 +4920,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -4929,13 +4929,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>535.0</v>
+        <v>1.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4946,7 +4946,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4955,13 +4955,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G183" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4981,10 +4981,10 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F184" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G184" t="n">
         <v>0.0</v>
@@ -5007,13 +5007,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F185" t="n">
-        <v>4.0</v>
+        <v>91.0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5033,13 +5033,13 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F186" t="n">
-        <v>91.0</v>
+        <v>2.0</v>
       </c>
       <c r="G186" t="n">
-        <v>64.0</v>
+        <v>12.0</v>
       </c>
       <c r="H186" t="n">
         <v>0.0</v>
@@ -5059,13 +5059,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F187" t="n">
-        <v>2.0</v>
+        <v>153.0</v>
       </c>
       <c r="G187" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5085,41 +5085,15 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F188" t="n">
-        <v>153.0</v>
+        <v>5.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>8</v>
-      </c>
-      <c r="B189" t="s">
-        <v>10</v>
-      </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>41</v>
-      </c>
-      <c r="E189" t="s">
-        <v>45</v>
-      </c>
-      <c r="F189" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H189" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -2179,7 +2179,7 @@
         <v>6.0</v>
       </c>
       <c r="G76" t="n">
-        <v>10038.0</v>
+        <v>8165.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>582436.0</v>
+        <v>580926.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -801,7 +801,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>139439.0</v>
+        <v>139325.0</v>
       </c>
       <c r="H23" t="n">
         <v>0.0</v>
@@ -2179,7 +2179,7 @@
         <v>6.0</v>
       </c>
       <c r="G76" t="n">
-        <v>8165.0</v>
+        <v>6323.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1815,7 +1815,7 @@
         <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>580926.0</v>
+        <v>580910.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1243,7 +1243,7 @@
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>15285.0</v>
+        <v>13538.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -4519,7 +4519,7 @@
         <v>471.0</v>
       </c>
       <c r="G166" t="n">
-        <v>5322.0</v>
+        <v>5310.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3632,7 +3632,7 @@
         <v>43</v>
       </c>
       <c r="F132" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G132" t="n">
         <v>11.0</v>
@@ -4545,7 +4545,7 @@
         <v>142.0</v>
       </c>
       <c r="G167" t="n">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -4620,7 +4620,7 @@
         <v>45</v>
       </c>
       <c r="F170" t="n">
-        <v>396.0</v>
+        <v>326.0</v>
       </c>
       <c r="G170" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1997,7 +1997,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>534439.0</v>
+        <v>541821.0</v>
       </c>
       <c r="H69" t="n">
         <v>66329.0</v>
@@ -2127,7 +2127,7 @@
         <v>44.0</v>
       </c>
       <c r="G74" t="n">
-        <v>35752.0</v>
+        <v>35742.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2179,7 +2179,7 @@
         <v>6.0</v>
       </c>
       <c r="G76" t="n">
-        <v>6323.0</v>
+        <v>6320.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -3375,7 +3375,7 @@
         <v>12.0</v>
       </c>
       <c r="G122" t="n">
-        <v>51.0</v>
+        <v>57.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3531,7 +3531,7 @@
         <v>35.0</v>
       </c>
       <c r="G128" t="n">
-        <v>17659.0</v>
+        <v>23619.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3866,7 +3866,7 @@
         <v>48</v>
       </c>
       <c r="F141" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -3996,10 +3996,10 @@
         <v>42</v>
       </c>
       <c r="F146" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G146" t="n">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4857,7 +4857,7 @@
         <v>3.0</v>
       </c>
       <c r="G179" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -5033,13 +5033,13 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F186" t="n">
-        <v>2.0</v>
+        <v>153.0</v>
       </c>
       <c r="G186" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H186" t="n">
         <v>0.0</v>
@@ -5059,10 +5059,10 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F187" t="n">
-        <v>153.0</v>
+        <v>5.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -5085,13 +5085,13 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F188" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H188" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1997,7 +1997,7 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>541821.0</v>
+        <v>541808.0</v>
       </c>
       <c r="H69" t="n">
         <v>66329.0</v>
@@ -2179,7 +2179,7 @@
         <v>6.0</v>
       </c>
       <c r="G76" t="n">
-        <v>6320.0</v>
+        <v>6312.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2855,7 +2855,7 @@
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>3474.0</v>
+        <v>1479.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -3089,7 +3089,7 @@
         <v>42.0</v>
       </c>
       <c r="G111" t="n">
-        <v>11839.0</v>
+        <v>11836.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3375,7 +3375,7 @@
         <v>12.0</v>
       </c>
       <c r="G122" t="n">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>580910.0</v>
+        <v>579043.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -4597,7 +4597,7 @@
         <v>31.0</v>
       </c>
       <c r="G169" t="n">
-        <v>663.0</v>
+        <v>651.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -1919,7 +1919,7 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1997,10 +1997,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>541808.0</v>
+        <v>542250.0</v>
       </c>
       <c r="H69" t="n">
-        <v>66329.0</v>
+        <v>65887.0</v>
       </c>
     </row>
     <row r="70">
@@ -4389,7 +4389,7 @@
         <v>1.0</v>
       </c>
       <c r="G161" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -4155,7 +4155,7 @@
         <v>38.0</v>
       </c>
       <c r="G152" t="n">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3245,7 +3245,7 @@
         <v>22.0</v>
       </c>
       <c r="G117" t="n">
-        <v>3824.0</v>
+        <v>4438.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3297,7 +3297,7 @@
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>922.0</v>
+        <v>308.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -847,13 +847,13 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>37865.0</v>
+        <v>3.0</v>
       </c>
       <c r="H25" t="n">
         <v>0.0</v>
@@ -864,7 +864,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -873,13 +873,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>30328.0</v>
+        <v>23455.0</v>
       </c>
       <c r="H26" t="n">
         <v>0.0</v>
@@ -899,13 +899,13 @@
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G27" t="n">
-        <v>15.0</v>
+        <v>30328.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -925,13 +925,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="H28" t="n">
         <v>0.0</v>
@@ -951,13 +951,13 @@
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H29" t="n">
         <v>0.0</v>
@@ -977,13 +977,13 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>60863.0</v>
+        <v>4.0</v>
       </c>
       <c r="H30" t="n">
         <v>0.0</v>
@@ -994,22 +994,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>5221.0</v>
+        <v>60863.0</v>
       </c>
       <c r="H31" t="n">
         <v>0.0</v>
@@ -1020,22 +1020,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>9.0</v>
+        <v>14410.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1055,13 +1055,13 @@
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>22287.0</v>
+        <v>5221.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1072,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1081,13 +1081,13 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>6198.0</v>
+        <v>9.0</v>
       </c>
       <c r="H34" t="n">
         <v>0.0</v>
@@ -1098,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -1107,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F35" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>22287.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1133,13 +1133,13 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0</v>
+        <v>185.0</v>
       </c>
       <c r="G36" t="n">
-        <v>43.0</v>
+        <v>6198.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1159,13 +1159,13 @@
         <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G37" t="n">
-        <v>32187.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1176,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -1185,13 +1185,13 @@
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>15723.0</v>
+        <v>43.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1202,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -1211,13 +1211,13 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.0</v>
+        <v>32187.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1237,13 +1237,13 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>13538.0</v>
+        <v>15723.0</v>
       </c>
       <c r="H40" t="n">
         <v>0.0</v>
@@ -1254,22 +1254,22 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
-        <v>354.0</v>
+        <v>0.0</v>
       </c>
       <c r="G41" t="n">
-        <v>3473.0</v>
+        <v>2.0</v>
       </c>
       <c r="H41" t="n">
         <v>0.0</v>
@@ -1280,22 +1280,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
       </c>
       <c r="F42" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="G42" t="n">
-        <v>10702.0</v>
+        <v>13538.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1315,13 +1315,13 @@
         <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0</v>
+        <v>354.0</v>
       </c>
       <c r="G43" t="n">
-        <v>5.0</v>
+        <v>3473.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -1341,13 +1341,13 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>81.0</v>
+        <v>15.0</v>
       </c>
       <c r="G44" t="n">
-        <v>23.0</v>
+        <v>5339.0</v>
       </c>
       <c r="H44" t="n">
         <v>0.0</v>
@@ -1358,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1373,7 +1373,7 @@
         <v>0.0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1393,13 +1393,13 @@
         <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>81.0</v>
       </c>
       <c r="G46" t="n">
-        <v>807.0</v>
+        <v>23.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1410,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -1419,13 +1419,13 @@
         <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>42583.0</v>
+        <v>2.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1436,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -1445,13 +1445,13 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>31.0</v>
+        <v>807.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1471,13 +1471,13 @@
         <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="G49" t="n">
-        <v>151149.0</v>
+        <v>42583.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1488,22 +1488,22 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="G50" t="n">
-        <v>7.0</v>
+        <v>32.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1514,22 +1514,22 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>28.0</v>
+        <v>156512.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1549,13 +1549,13 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0</v>
+        <v>28.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H52" t="n">
         <v>0.0</v>
@@ -1575,13 +1575,13 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G53" t="n">
-        <v>4.0</v>
+        <v>28.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F54" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1624,16 +1624,16 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G55" t="n">
-        <v>31.0</v>
+        <v>4.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1653,10 +1653,10 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F56" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1679,13 +1679,13 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1705,13 +1705,13 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G58" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1722,22 +1722,22 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1748,22 +1748,22 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F60" t="n">
         <v>0.0</v>
       </c>
       <c r="G60" t="n">
-        <v>26.0</v>
+        <v>36.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -1783,13 +1783,13 @@
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1800,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -1809,13 +1809,13 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F62" t="n">
         <v>0.0</v>
       </c>
       <c r="G62" t="n">
-        <v>12.0</v>
+        <v>26.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1835,13 +1835,13 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="G63" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1852,7 +1852,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -1861,13 +1861,13 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1878,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -1887,13 +1887,13 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
         <v>0.0</v>
       </c>
       <c r="G65" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1913,13 +1913,13 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G66" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1933,22 +1933,22 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
       </c>
       <c r="G67" t="n">
-        <v>162125.0</v>
+        <v>5.0</v>
       </c>
       <c r="H67" t="n">
-        <v>73361.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1959,22 +1959,22 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
       </c>
       <c r="G68" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
       <c r="H68" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1991,16 +1991,16 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
       </c>
       <c r="G69" t="n">
-        <v>542250.0</v>
+        <v>162125.0</v>
       </c>
       <c r="H69" t="n">
-        <v>65887.0</v>
+        <v>73361.0</v>
       </c>
     </row>
     <row r="70">
@@ -2014,19 +2014,19 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F70" t="n">
         <v>0.0</v>
       </c>
       <c r="G70" t="n">
-        <v>119869.0</v>
+        <v>35.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="71">
@@ -2040,19 +2040,19 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
         <v>0.0</v>
       </c>
       <c r="G71" t="n">
-        <v>3.0</v>
+        <v>542250.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>65887.0</v>
       </c>
     </row>
     <row r="72">
@@ -2069,13 +2069,13 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
       </c>
       <c r="G72" t="n">
-        <v>141196.0</v>
+        <v>119869.0</v>
       </c>
       <c r="H72" t="n">
         <v>0.0</v>
@@ -2092,16 +2092,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>78.0</v>
+        <v>0.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2118,16 +2118,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F74" t="n">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
       <c r="G74" t="n">
-        <v>35742.0</v>
+        <v>141196.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2147,13 +2147,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F75" t="n">
-        <v>3.0</v>
+        <v>78.0</v>
       </c>
       <c r="G75" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2173,13 +2173,13 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F76" t="n">
-        <v>6.0</v>
+        <v>44.0</v>
       </c>
       <c r="G76" t="n">
-        <v>6312.0</v>
+        <v>35742.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2199,16 +2199,16 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G77" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="H77" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2216,22 +2216,22 @@
         <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G78" t="n">
-        <v>12.0</v>
+        <v>6312.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2242,25 +2242,25 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="80">
@@ -2277,13 +2277,13 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>30772.0</v>
+        <v>79.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2294,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2303,13 +2303,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G81" t="n">
-        <v>8325.0</v>
+        <v>0.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2329,13 +2329,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2355,13 +2355,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>61.0</v>
+        <v>21.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2381,13 +2381,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>21.0</v>
+        <v>245.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2398,7 +2398,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2407,13 +2407,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G85" t="n">
-        <v>278.0</v>
+        <v>43.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2433,13 +2433,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F86" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G86" t="n">
-        <v>31.0</v>
+        <v>17.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2465,7 +2465,7 @@
         <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>34579.0</v>
+        <v>65351.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2491,7 +2491,7 @@
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>37378.0</v>
+        <v>45657.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2699,7 +2699,7 @@
         <v>6.0</v>
       </c>
       <c r="G96" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2829,7 +2829,7 @@
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -4831,7 +4831,7 @@
         <v>13.0</v>
       </c>
       <c r="G178" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4857,7 +4857,7 @@
         <v>3.0</v>
       </c>
       <c r="G179" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4909,7 +4909,7 @@
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>535.0</v>
+        <v>508.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4929,13 +4929,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4946,7 +4946,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4955,13 +4955,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F183" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G183" t="n">
         <v>5.0</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4972,7 +4972,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -4981,13 +4981,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F184" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -5007,13 +5007,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F185" t="n">
-        <v>91.0</v>
+        <v>5.0</v>
       </c>
       <c r="G185" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5033,10 +5033,10 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F186" t="n">
-        <v>153.0</v>
+        <v>4.0</v>
       </c>
       <c r="G186" t="n">
         <v>0.0</v>
@@ -5059,13 +5059,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F187" t="n">
-        <v>5.0</v>
+        <v>91.0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5085,15 +5085,67 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
+        <v>44</v>
+      </c>
+      <c r="F188" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" t="s">
+        <v>45</v>
+      </c>
+      <c r="F189" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" t="s">
         <v>43</v>
       </c>
-      <c r="F188" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G188" t="n">
+      <c r="F190" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G190" t="n">
         <v>12.0</v>
       </c>
-      <c r="H188" t="n">
+      <c r="H190" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -3401,7 +3401,7 @@
         <v>241.0</v>
       </c>
       <c r="G123" t="n">
-        <v>579043.0</v>
+        <v>579042.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>

--- a/Download/Capi_ZR.xlsx
+++ b/Download/Capi_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="50">
   <si>
     <t>Area</t>
   </si>
@@ -2251,16 +2251,16 @@
         <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
       </c>
       <c r="G79" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2268,25 +2268,25 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
         <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F80" t="n">
         <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>79.0</v>
+        <v>13.0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="81">
@@ -2294,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
         <v>15</v>
@@ -2303,13 +2303,13 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F81" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>79.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2329,13 +2329,13 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>20.0</v>
+        <v>8.0</v>
       </c>
       <c r="G82" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2355,13 +2355,13 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="G83" t="n">
-        <v>21.0</v>
+        <v>61.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2381,13 +2381,13 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>245.0</v>
+        <v>21.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2398,7 +2398,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
         <v>15</v>
@@ -2407,13 +2407,13 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F85" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" t="n">
-        <v>43.0</v>
+        <v>245.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2433,13 +2433,13 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G86" t="n">
-        <v>17.0</v>
+        <v>43.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2459,13 +2459,13 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F87" t="n">
         <v>0.0</v>
       </c>
       <c r="G87" t="n">
-        <v>65351.0</v>
+        <v>17.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2485,13 +2485,13 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F88" t="n">
         <v>0.0</v>
       </c>
       <c r="G88" t="n">
-        <v>45657.0</v>
+        <v>65351.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2508,16 +2508,16 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F89" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>45657.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2537,16 +2537,16 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G90" t="n">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="91">
@@ -2563,16 +2563,16 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="G91" t="n">
-        <v>139.0</v>
+        <v>45.0</v>
       </c>
       <c r="H91" t="n">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="92">
@@ -2589,16 +2589,16 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F92" t="n">
         <v>0.0</v>
       </c>
       <c r="G92" t="n">
-        <v>66.0</v>
+        <v>139.0</v>
       </c>
       <c r="H92" t="n">
-        <v>2.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="93">
@@ -2615,16 +2615,16 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F93" t="n">
         <v>0.0</v>
       </c>
       <c r="G93" t="n">
-        <v>26.0</v>
+        <v>66.0</v>
       </c>
       <c r="H93" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="94">
@@ -2632,13 +2632,13 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
         <v>42</v>
@@ -2647,10 +2647,10 @@
         <v>0.0</v>
       </c>
       <c r="G94" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="95">
@@ -2667,13 +2667,13 @@
         <v>31</v>
       </c>
       <c r="E95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F95" t="n">
         <v>0.0</v>
       </c>
       <c r="G95" t="n">
-        <v>3393.0</v>
+        <v>14.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2684,7 +2684,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -2693,13 +2693,13 @@
         <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G96" t="n">
-        <v>24.0</v>
+        <v>3393.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2719,13 +2719,13 @@
         <v>31</v>
       </c>
       <c r="E97" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G97" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2745,13 +2745,13 @@
         <v>31</v>
       </c>
       <c r="E98" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F98" t="n">
         <v>0.0</v>
       </c>
       <c r="G98" t="n">
-        <v>88.0</v>
+        <v>8.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2771,13 +2771,13 @@
         <v>31</v>
       </c>
       <c r="E99" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F99" t="n">
         <v>0.0</v>
       </c>
       <c r="G99" t="n">
-        <v>4984.0</v>
+        <v>88.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2797,13 +2797,13 @@
         <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F100" t="n">
         <v>0.0</v>
       </c>
       <c r="G100" t="n">
-        <v>3913.0</v>
+        <v>4984.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2823,13 +2823,13 @@
         <v>31</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F101" t="n">
         <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>17.0</v>
+        <v>3913.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2849,13 +2849,13 @@
         <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1479.0</v>
+        <v>17.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2866,25 +2866,25 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n">
-        <v>6.0</v>
+        <v>1479.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2901,16 +2901,16 @@
         <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G104" t="n">
-        <v>381.0</v>
+        <v>6.0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="105">
@@ -2927,13 +2927,13 @@
         <v>32</v>
       </c>
       <c r="E105" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F105" t="n">
         <v>0.0</v>
       </c>
       <c r="G105" t="n">
-        <v>265.0</v>
+        <v>381.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2944,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -2953,13 +2953,13 @@
         <v>32</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
       </c>
       <c r="G106" t="n">
-        <v>70.0</v>
+        <v>265.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2979,16 +2979,16 @@
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>3.0</v>
+        <v>70.0</v>
       </c>
       <c r="H107" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -2996,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -3005,16 +3005,16 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F108" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="109">
@@ -3031,13 +3031,13 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F109" t="n">
-        <v>147.0</v>
+        <v>12.0</v>
       </c>
       <c r="G109" t="n">
-        <v>3034.0</v>
+        <v>0.0</v>
       </c>
       <c r="H109" t="n">
         <v>0.0</v>
@@ -3057,13 +3057,13 @@
         <v>32</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F110" t="n">
-        <v>19.0</v>
+        <v>147.0</v>
       </c>
       <c r="G110" t="n">
-        <v>19.0</v>
+        <v>3034.0</v>
       </c>
       <c r="H110" t="n">
         <v>0.0</v>
@@ -3083,13 +3083,13 @@
         <v>32</v>
       </c>
       <c r="E111" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>42.0</v>
+        <v>19.0</v>
       </c>
       <c r="G111" t="n">
-        <v>11836.0</v>
+        <v>19.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3100,22 +3100,22 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E112" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="G112" t="n">
-        <v>23875.0</v>
+        <v>11836.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3135,13 +3135,13 @@
         <v>33</v>
       </c>
       <c r="E113" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F113" t="n">
-        <v>6.0</v>
+        <v>45.0</v>
       </c>
       <c r="G113" t="n">
-        <v>4.0</v>
+        <v>23875.0</v>
       </c>
       <c r="H113" t="n">
         <v>0.0</v>
@@ -3161,13 +3161,13 @@
         <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>737.0</v>
+        <v>6.0</v>
       </c>
       <c r="G114" t="n">
-        <v>48265.0</v>
+        <v>4.0</v>
       </c>
       <c r="H114" t="n">
         <v>0.0</v>
@@ -3187,13 +3187,13 @@
         <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F115" t="n">
-        <v>4.0</v>
+        <v>737.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>48265.0</v>
       </c>
       <c r="H115" t="n">
         <v>0.0</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
         <v>16</v>
@@ -3213,10 +3213,10 @@
         <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F116" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -3239,13 +3239,13 @@
         <v>33</v>
       </c>
       <c r="E117" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F117" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
       <c r="G117" t="n">
-        <v>4438.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3265,13 +3265,13 @@
         <v>33</v>
       </c>
       <c r="E118" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="G118" t="n">
-        <v>3.0</v>
+        <v>4438.0</v>
       </c>
       <c r="H118" t="n">
         <v>0.0</v>
@@ -3291,13 +3291,13 @@
         <v>33</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
       </c>
       <c r="G119" t="n">
-        <v>308.0</v>
+        <v>3.0</v>
       </c>
       <c r="H119" t="n">
         <v>0.0</v>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -3317,16 +3317,16 @@
         <v>33</v>
       </c>
       <c r="E120" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>308.0</v>
       </c>
       <c r="H120" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3343,16 +3343,16 @@
         <v>33</v>
       </c>
       <c r="E121" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F121" t="n">
-        <v>1518.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
-        <v>210270.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="122">
@@ -3369,13 +3369,13 @@
         <v>33</v>
       </c>
       <c r="E122" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F122" t="n">
-        <v>12.0</v>
+        <v>1518.0</v>
       </c>
       <c r="G122" t="n">
-        <v>54.0</v>
+        <v>210270.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3395,13 +3395,13 @@
         <v>33</v>
       </c>
       <c r="E123" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
-        <v>241.0</v>
+        <v>12.0</v>
       </c>
       <c r="G123" t="n">
-        <v>579042.0</v>
+        <v>54.0</v>
       </c>
       <c r="H123" t="n">
         <v>0.0</v>
@@ -3421,13 +3421,13 @@
         <v>33</v>
       </c>
       <c r="E124" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F124" t="n">
-        <v>4.0</v>
+        <v>241.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>579042.0</v>
       </c>
       <c r="H124" t="n">
         <v>0.0</v>
@@ -3444,16 +3444,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F125" t="n">
         <v>4.0</v>
       </c>
       <c r="G125" t="n">
-        <v>81.0</v>
+        <v>0.0</v>
       </c>
       <c r="H125" t="n">
         <v>0.0</v>
@@ -3473,13 +3473,13 @@
         <v>34</v>
       </c>
       <c r="E126" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F126" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>81.0</v>
       </c>
       <c r="H126" t="n">
         <v>0.0</v>
@@ -3499,13 +3499,13 @@
         <v>34</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H127" t="n">
         <v>0.0</v>
@@ -3525,13 +3525,13 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F128" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="G128" t="n">
-        <v>23619.0</v>
+        <v>7.0</v>
       </c>
       <c r="H128" t="n">
         <v>0.0</v>
@@ -3548,16 +3548,16 @@
         <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="G129" t="n">
-        <v>7663.0</v>
+        <v>23619.0</v>
       </c>
       <c r="H129" t="n">
         <v>0.0</v>
@@ -3577,16 +3577,16 @@
         <v>35</v>
       </c>
       <c r="E130" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
       </c>
       <c r="G130" t="n">
-        <v>18.0</v>
+        <v>7663.0</v>
       </c>
       <c r="H130" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -3603,16 +3603,16 @@
         <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
       </c>
       <c r="G131" t="n">
-        <v>16248.0</v>
+        <v>18.0</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="132">
@@ -3620,22 +3620,22 @@
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
       </c>
       <c r="G132" t="n">
-        <v>11.0</v>
+        <v>16248.0</v>
       </c>
       <c r="H132" t="n">
         <v>0.0</v>
@@ -3646,7 +3646,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3655,13 +3655,13 @@
         <v>36</v>
       </c>
       <c r="E133" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F133" t="n">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="H133" t="n">
         <v>0.0</v>
@@ -3681,13 +3681,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F134" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="G134" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H134" t="n">
         <v>0.0</v>
@@ -3707,13 +3707,13 @@
         <v>36</v>
       </c>
       <c r="E135" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F135" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H135" t="n">
         <v>0.0</v>
@@ -3733,13 +3733,13 @@
         <v>36</v>
       </c>
       <c r="E136" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F136" t="n">
-        <v>1770.0</v>
+        <v>16.0</v>
       </c>
       <c r="G136" t="n">
-        <v>3356.0</v>
+        <v>0.0</v>
       </c>
       <c r="H136" t="n">
         <v>0.0</v>
@@ -3759,13 +3759,13 @@
         <v>36</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F137" t="n">
-        <v>46.0</v>
+        <v>1770.0</v>
       </c>
       <c r="G137" t="n">
-        <v>69.0</v>
+        <v>3356.0</v>
       </c>
       <c r="H137" t="n">
         <v>0.0</v>
@@ -3785,13 +3785,13 @@
         <v>36</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F138" t="n">
-        <v>6.0</v>
+        <v>46.0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0</v>
+        <v>69.0</v>
       </c>
       <c r="H138" t="n">
         <v>0.0</v>
@@ -3811,13 +3811,13 @@
         <v>36</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F139" t="n">
-        <v>184.0</v>
+        <v>6.0</v>
       </c>
       <c r="G139" t="n">
-        <v>667.0</v>
+        <v>0.0</v>
       </c>
       <c r="H139" t="n">
         <v>0.0</v>
@@ -3837,16 +3837,16 @@
         <v>36</v>
       </c>
       <c r="E140" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F140" t="n">
-        <v>201.0</v>
+        <v>184.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>667.0</v>
       </c>
       <c r="H140" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="141">
@@ -3854,25 +3854,25 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E141" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F141" t="n">
-        <v>4.0</v>
+        <v>201.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="142">
@@ -3889,13 +3889,13 @@
         <v>37</v>
       </c>
       <c r="E142" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H142" t="n">
         <v>0.0</v>
@@ -3915,7 +3915,7 @@
         <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
@@ -3941,13 +3941,13 @@
         <v>37</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F144" t="n">
         <v>0.0</v>
       </c>
       <c r="G144" t="n">
-        <v>49.0</v>
+        <v>7.0</v>
       </c>
       <c r="H144" t="n">
         <v>0.0</v>
@@ -3958,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3967,13 +3967,13 @@
         <v>37</v>
       </c>
       <c r="E145" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F145" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="H145" t="n">
         <v>0.0</v>
@@ -3993,13 +3993,13 @@
         <v>37</v>
       </c>
       <c r="E146" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F146" t="n">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="G146" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
       <c r="H146" t="n">
         <v>0.0</v>
@@ -4019,13 +4019,13 @@
         <v>37</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F147" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="H147" t="n">
         <v>0.0</v>
@@ -4045,13 +4045,13 @@
         <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G148" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n">
         <v>0.0</v>
@@ -4071,13 +4071,13 @@
         <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F149" t="n">
         <v>0.0</v>
       </c>
       <c r="G149" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H149" t="n">
         <v>0.0</v>
@@ -4097,13 +4097,13 @@
         <v>37</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F150" t="n">
         <v>0.0</v>
       </c>
       <c r="G150" t="n">
-        <v>118.0</v>
+        <v>9.0</v>
       </c>
       <c r="H150" t="n">
         <v>0.0</v>
@@ -4114,7 +4114,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -4123,13 +4123,13 @@
         <v>37</v>
       </c>
       <c r="E151" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F151" t="n">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>118.0</v>
       </c>
       <c r="H151" t="n">
         <v>0.0</v>
@@ -4140,22 +4140,22 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
         <v>46</v>
       </c>
       <c r="F152" t="n">
-        <v>38.0</v>
+        <v>60.0</v>
       </c>
       <c r="G152" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n">
         <v>0.0</v>
@@ -4175,13 +4175,13 @@
         <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F153" t="n">
-        <v>1.0</v>
+        <v>38.0</v>
       </c>
       <c r="G153" t="n">
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="H153" t="n">
         <v>0.0</v>
@@ -4201,13 +4201,13 @@
         <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="H154" t="n">
         <v>0.0</v>
@@ -4227,13 +4227,13 @@
         <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F155" t="n">
         <v>0.0</v>
       </c>
       <c r="G155" t="n">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="H155" t="n">
         <v>0.0</v>
@@ -4244,7 +4244,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4253,13 +4253,13 @@
         <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F156" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="G156" t="n">
-        <v>27.0</v>
+        <v>15.0</v>
       </c>
       <c r="H156" t="n">
         <v>0.0</v>
@@ -4279,13 +4279,13 @@
         <v>38</v>
       </c>
       <c r="E157" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F157" t="n">
-        <v>4.0</v>
+        <v>51.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="H157" t="n">
         <v>0.0</v>
@@ -4305,13 +4305,13 @@
         <v>38</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G158" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H158" t="n">
         <v>0.0</v>
@@ -4331,13 +4331,13 @@
         <v>38</v>
       </c>
       <c r="E159" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F159" t="n">
         <v>0.0</v>
       </c>
       <c r="G159" t="n">
-        <v>31.0</v>
+        <v>3.0</v>
       </c>
       <c r="H159" t="n">
         <v>0.0</v>
@@ -4348,22 +4348,22 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F160" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="H160" t="n">
         <v>0.0</v>
@@ -4383,13 +4383,13 @@
         <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G161" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="H161" t="n">
         <v>0.0</v>
@@ -4409,10 +4409,10 @@
         <v>39</v>
       </c>
       <c r="E162" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G162" t="n">
         <v>16.0</v>
@@ -4435,13 +4435,13 @@
         <v>39</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F163" t="n">
         <v>0.0</v>
       </c>
       <c r="G163" t="n">
-        <v>51.0</v>
+        <v>16.0</v>
       </c>
       <c r="H163" t="n">
         <v>0.0</v>
@@ -4452,7 +4452,7 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -4461,13 +4461,13 @@
         <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F164" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>51.0</v>
       </c>
       <c r="H164" t="n">
         <v>0.0</v>
@@ -4487,13 +4487,13 @@
         <v>39</v>
       </c>
       <c r="E165" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F165" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G165" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" t="n">
         <v>0.0</v>
@@ -4513,13 +4513,13 @@
         <v>39</v>
       </c>
       <c r="E166" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F166" t="n">
-        <v>471.0</v>
+        <v>4.0</v>
       </c>
       <c r="G166" t="n">
-        <v>5310.0</v>
+        <v>4.0</v>
       </c>
       <c r="H166" t="n">
         <v>0.0</v>
@@ -4539,13 +4539,13 @@
         <v>39</v>
       </c>
       <c r="E167" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
-        <v>142.0</v>
+        <v>471.0</v>
       </c>
       <c r="G167" t="n">
-        <v>64.0</v>
+        <v>5310.0</v>
       </c>
       <c r="H167" t="n">
         <v>0.0</v>
@@ -4565,13 +4565,13 @@
         <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F168" t="n">
-        <v>3.0</v>
+        <v>142.0</v>
       </c>
       <c r="G168" t="n">
-        <v>7.0</v>
+        <v>64.0</v>
       </c>
       <c r="H168" t="n">
         <v>0.0</v>
@@ -4591,13 +4591,13 @@
         <v>39</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>31.0</v>
+        <v>3.0</v>
       </c>
       <c r="G169" t="n">
-        <v>651.0</v>
+        <v>7.0</v>
       </c>
       <c r="H169" t="n">
         <v>0.0</v>
@@ -4617,13 +4617,13 @@
         <v>39</v>
       </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>326.0</v>
+        <v>31.0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0</v>
+        <v>651.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -4634,19 +4634,19 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
       </c>
       <c r="D171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E171" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F171" t="n">
-        <v>9.0</v>
+        <v>326.0</v>
       </c>
       <c r="G171" t="n">
         <v>0.0</v>
@@ -4669,10 +4669,10 @@
         <v>40</v>
       </c>
       <c r="E172" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
-        <v>155.0</v>
+        <v>9.0</v>
       </c>
       <c r="G172" t="n">
         <v>0.0</v>
@@ -4695,13 +4695,13 @@
         <v>40</v>
       </c>
       <c r="E173" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F173" t="n">
-        <v>4.0</v>
+        <v>155.0</v>
       </c>
       <c r="G173" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="H173" t="n">
         <v>0.0</v>
@@ -4721,13 +4721,13 @@
         <v>40</v>
       </c>
       <c r="E174" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F174" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G174" t="n">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="H174" t="n">
         <v>0.0</v>
@@ -4747,13 +4747,13 @@
         <v>40</v>
       </c>
       <c r="E175" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F175" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H175" t="n">
         <v>0.0</v>
@@ -4764,7 +4764,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4773,10 +4773,10 @@
         <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F176" t="n">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -4799,13 +4799,13 @@
         <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="G177" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H177" t="n">
         <v>0.0</v>
@@ -4816,22 +4816,22 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
       </c>
       <c r="D178" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E178" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F178" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="G178" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H178" t="n">
         <v>0.0</v>
@@ -4851,13 +4851,13 @@
         <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F179" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="G179" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H179" t="n">
         <v>0.0</v>
@@ -4877,13 +4877,13 @@
         <v>41</v>
       </c>
       <c r="E180" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G180" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H180" t="n">
         <v>0.0</v>
@@ -4903,13 +4903,13 @@
         <v>41</v>
       </c>
       <c r="E181" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F181" t="n">
         <v>0.0</v>
       </c>
       <c r="G181" t="n">
-        <v>508.0</v>
+        <v>4.0</v>
       </c>
       <c r="H181" t="n">
         <v>0.0</v>
@@ -4920,7 +4920,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -4929,13 +4929,13 @@
         <v>41</v>
       </c>
       <c r="E182" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F182" t="n">
         <v>0.0</v>
       </c>
       <c r="G182" t="n">
-        <v>4.0</v>
+        <v>508.0</v>
       </c>
       <c r="H182" t="n">
         <v>0.0</v>
@@ -4955,13 +4955,13 @@
         <v>41</v>
       </c>
       <c r="E183" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F183" t="n">
         <v>0.0</v>
       </c>
       <c r="G183" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H183" t="n">
         <v>0.0</v>
@@ -4981,13 +4981,13 @@
         <v>41</v>
       </c>
       <c r="E184" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F184" t="n">
         <v>0.0</v>
       </c>
       <c r="G184" t="n">
-        <v>27.0</v>
+        <v>5.0</v>
       </c>
       <c r="H184" t="n">
         <v>0.0</v>
@@ -4998,7 +4998,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
         <v>17</v>
@@ -5007,13 +5007,13 @@
         <v>41</v>
       </c>
       <c r="E185" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F185" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="H185" t="n">
         <v>0.0</v>
@@ -5033,10 +5033,10 @@
         <v>41</v>
       </c>
       <c r="E186" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F186" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G186" t="n">
         <v>0.0</v>
@@ -5059,13 +5059,13 @@
         <v>41</v>
       </c>
       <c r="E187" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F187" t="n">
-        <v>91.0</v>
+        <v>4.0</v>
       </c>
       <c r="G187" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
       <c r="H187" t="n">
         <v>0.0</v>
@@ -5085,13 +5085,13 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F188" t="n">
-        <v>153.0</v>
+        <v>91.0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
       <c r="H188" t="n">
         <v>0.0</v>
@@ -5111,10 +5111,10 @@
         <v>41</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F189" t="n">
-        <v>5.0</v>
+        <v>153.0</v>
       </c>
       <c r="G189" t="n">
         <v>0.0</v>
@@ -5137,15 +5137,41 @@
         <v>41</v>
       </c>
       <c r="E190" t="s">
+        <v>45</v>
+      </c>
+      <c r="F190" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" t="s">
         <v>43</v>
       </c>
-      <c r="F190" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G190" t="n">
+      <c r="F191" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G191" t="n">
         <v>12.0</v>
       </c>
-      <c r="H190" t="n">
+      <c r="H191" t="n">
         <v>0.0</v>
       </c>
     </row>
